--- a/UploadTemplates/addAutomailTemplate.xlsx
+++ b/UploadTemplates/addAutomailTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>RID</t>
   </si>
@@ -32,13 +32,16 @@
   </si>
   <si>
     <t>Signature</t>
+  </si>
+  <si>
+    <t>Send Date Calc Factor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -46,13 +49,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF262626"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -67,8 +82,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -373,30 +390,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/UploadTemplates/addAutomailTemplate.xlsx
+++ b/UploadTemplates/addAutomailTemplate.xlsx
@@ -34,7 +34,7 @@
     <t>Signature</t>
   </si>
   <si>
-    <t>Send Date Calc Factor</t>
+    <t>Send_Date_Calc_Factor</t>
   </si>
 </sst>
 </file>
